--- a/stuff/source_merit_ranking.xlsx
+++ b/stuff/source_merit_ranking.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="What sources say" sheetId="1" r:id="R5b8995d90bb4478b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranked sources" sheetId="2" r:id="Re84f83471f1749a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical evidence" sheetId="3" r:id="Rf91f434134af4cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix criteria" sheetId="4" r:id="Rb0c67923a356475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="5" r:id="R40d7899e380b484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="What sources say" sheetId="1" r:id="R9ccf85077990493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranked sources" sheetId="2" r:id="Rd4d3e8d23f344092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical evidence" sheetId="3" r:id="R99b018903b8b42e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix criteria" sheetId="4" r:id="Rf4ae61fe7f6842f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="5" r:id="Raac55d77839d409c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -822,10 +822,10 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
-        <x:v>• ERC Advanced Grants: Nearly €840 million to support Europe’s leading researchers.</x:v>
+        <x:v>• The ERC awarded €838 million to 319 leading researchers across Europe under Horizon Europe, financing ambitious frontier-research projects and teams based in Europe.</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
-        <x:v>ERC Advanced Grants: Nearly €840 million to support Europe’s leading researchers.</x:v>
+        <x:v>EU frontier-research funding directly strengthens Europe’s resident research workforce and knowledge base.</x:v>
       </x:c>
       <x:c r="G17" s="13" t="str">
         <x:v>97 · A — Highest authority</x:v>
@@ -6075,7 +6075,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19f9a987d1354d09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23f9ecbfc81d4595"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7185,10 +7185,10 @@
         <x:v>4-month core</x:v>
       </x:c>
       <x:c r="T17" s="13" t="str">
-        <x:v>Strength from outside</x:v>
+        <x:v>Build and keep talent</x:v>
       </x:c>
       <x:c r="U17" s="13" t="str">
-        <x:v>• ERC Advanced Grants: Nearly €840 million to support Europe’s leading researchers.</x:v>
+        <x:v>• The ERC awarded €838 million to 319 leading researchers across Europe under Horizon Europe, financing ambitious frontier-research projects and teams based in Europe.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="70" customHeight="1">
@@ -16722,7 +16722,9 @@
       <x:c r="S166" s="13" t="str">
         <x:v>4-month core</x:v>
       </x:c>
-      <x:c r="T166" s="13" t="str"/>
+      <x:c r="T166" s="13" t="str">
+        <x:v>Build and keep talent</x:v>
+      </x:c>
       <x:c r="U166" s="13" t="str">
         <x:v>• Cross-border and cross-sector researcher mobility, implemented through the Horizon Europe EdTech Talents project, contributes to the professional development of educational researchers beyond traditional academic performance indicators.
 • The study offers actionable insights for policymakers and research organizations designing mobility schemes aimed at strengthening innovation ecosystems and promoting sustainable knowledge circulation.</x:v>
@@ -19702,7 +19704,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca50d823cd949db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a54c2900f74da5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21291,10 +21293,10 @@
         <x:v>reviewed_pass_weak_signal_primary_resolved</x:v>
       </x:c>
       <x:c r="P17" s="13" t="str">
-        <x:v>ERC Advanced Grants: Nearly €840 million to support Europe’s leading researchers.</x:v>
+        <x:v>EU frontier-research funding directly strengthens Europe’s resident research workforce and knowledge base.</x:v>
       </x:c>
       <x:c r="Q17" s="13" t="str">
-        <x:v>• ERC Advanced Grants: Nearly €840 million to support Europe’s leading researchers.</x:v>
+        <x:v>• The ERC awarded €838 million to 319 leading researchers across Europe under Horizon Europe, financing ambitious frontier-research projects and teams based in Europe.</x:v>
       </x:c>
       <x:c r="R17" s="13" t="str"/>
       <x:c r="S17" s="13" t="str"/>
@@ -21305,13 +21307,13 @@
         <x:v>People &amp; knowledge</x:v>
       </x:c>
       <x:c r="X17" s="13" t="str">
-        <x:v>C — Stronger, but reliant</x:v>
+        <x:v>A — More control, stronger</x:v>
       </x:c>
       <x:c r="Y17" s="13" t="str">
-        <x:v>Strength from outside</x:v>
+        <x:v>Build and keep talent</x:v>
       </x:c>
       <x:c r="Z17" s="13" t="str">
-        <x:v>The ERC release reports increased applications from researchers outside Europe and a smaller realised relocation flow. Those relocations strengthen European research capability, but the marginal talent input is externally sourced and depends on continued attraction and retention, so the observed mechanism is K-C.</x:v>
+        <x:v>The ERC awarded €838 million to 319 leading researchers across Europe under Horizon Europe. The grants finance ambitious frontier-research projects and research teams based across Europe, directly strengthening the European research workforce and knowledge base.</x:v>
       </x:c>
       <x:c r="AA17" s="13" t="n">
         <x:v>82</x:v>
@@ -33979,13 +33981,27 @@
       <x:c r="T166" s="13" t="str"/>
       <x:c r="U166" s="13" t="str"/>
       <x:c r="V166" s="13" t="str"/>
-      <x:c r="W166" s="13" t="str"/>
-      <x:c r="X166" s="13" t="str"/>
-      <x:c r="Y166" s="13" t="str"/>
-      <x:c r="Z166" s="13" t="str"/>
-      <x:c r="AA166" s="13" t="str"/>
-      <x:c r="AB166" s="13" t="str"/>
-      <x:c r="AC166" s="13" t="str"/>
+      <x:c r="W166" s="13" t="str">
+        <x:v>People &amp; knowledge</x:v>
+      </x:c>
+      <x:c r="X166" s="13" t="str">
+        <x:v>A — More control, stronger</x:v>
+      </x:c>
+      <x:c r="Y166" s="13" t="str">
+        <x:v>Build and keep talent</x:v>
+      </x:c>
+      <x:c r="Z166" s="13" t="str">
+        <x:v>The Horizon Europe EdTech Talents project uses reciprocal cross-border and cross-sector secondments across European research systems to build researchers’ skills, professional networks and applied knowledge. The study finds that this mobility supports professional development and brain circulation, including in widening research systems, strengthening Europe’s own research workforce and knowledge base.</x:v>
+      </x:c>
+      <x:c r="AA166" s="13" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="AB166" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AC166" s="13" t="str">
+        <x:v>stay strong</x:v>
+      </x:c>
       <x:c r="AD166" s="13" t="str"/>
       <x:c r="AE166" s="13" t="str"/>
       <x:c r="AF166" s="13" t="str">
@@ -37831,7 +37847,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R541017f4a7bb40dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56ef4a83507a4220"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38228,7 +38244,7 @@
         <x:v>Current radar state</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>2026-08-29T05:52Z · A=182 · B=24 · C=14 · Matrix findings=38</x:v>
+        <x:v>2026-08-29T05:52Z · A=182 · B=24 · C=14 · Matrix findings=39</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
@@ -38416,7 +38432,7 @@
         <x:v>Matrix profile version</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
-        <x:v>v17.13.26-balanced-semantic-contract</x:v>
+        <x:v>v17.13.29-talent-capability-evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="38" customHeight="1">
